--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,596 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133729096</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92217</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>658</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>550668</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6998719</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133729086</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>550739</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6998590</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133729090</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>550845</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6998741</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133729089</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>550773</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6998677</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133729088</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>550773</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6998677</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133729087</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99152</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>550719</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6998593</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>133729096</v>
       </c>
       <c r="B3" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>133729086</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>133729090</v>
       </c>
       <c r="B5" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>133729089</v>
       </c>
       <c r="B6" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>133729087</v>
       </c>
       <c r="B8" t="n">
-        <v>99152</v>
+        <v>99154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>133729096</v>
       </c>
       <c r="B3" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>133729086</v>
       </c>
       <c r="B4" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>133729087</v>
       </c>
       <c r="B8" t="n">
-        <v>99154</v>
+        <v>99162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>133729096</v>
       </c>
       <c r="B3" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>133729086</v>
       </c>
       <c r="B4" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>133729090</v>
       </c>
       <c r="B5" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>133729089</v>
       </c>
       <c r="B6" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>133729088</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>133729087</v>
       </c>
       <c r="B8" t="n">
-        <v>99162</v>
+        <v>99190</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>133729096</v>
       </c>
       <c r="B3" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>133729086</v>
       </c>
       <c r="B4" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>133729090</v>
       </c>
       <c r="B5" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>133729089</v>
       </c>
       <c r="B6" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>133729088</v>
       </c>
       <c r="B7" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>133729087</v>
       </c>
       <c r="B8" t="n">
-        <v>99190</v>
+        <v>99200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>133729096</v>
       </c>
       <c r="B3" t="n">
-        <v>92228</v>
+        <v>92230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>133729086</v>
       </c>
       <c r="B4" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>133729090</v>
       </c>
       <c r="B5" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>133729089</v>
       </c>
       <c r="B6" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>133729087</v>
       </c>
       <c r="B8" t="n">
-        <v>99200</v>
+        <v>99202</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -1184,53 +1184,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133729088</v>
+        <v>133729087</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>99203</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Granliden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550773</v>
+        <v>550719</v>
       </c>
       <c r="R7" t="n">
-        <v>6998677</v>
+        <v>6998593</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,45 +1281,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133729087</v>
+        <v>133729088</v>
       </c>
       <c r="B8" t="n">
-        <v>99203</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Granliden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550719</v>
+        <v>550773</v>
       </c>
       <c r="R8" t="n">
-        <v>6998593</v>
+        <v>6998677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>133729096</v>
       </c>
       <c r="B3" t="n">
-        <v>92231</v>
+        <v>92238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>133729086</v>
       </c>
       <c r="B4" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>133729090</v>
       </c>
       <c r="B5" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>133729089</v>
       </c>
       <c r="B6" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>133729087</v>
       </c>
       <c r="B7" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>6768426</v>
       </c>
       <c r="B2" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550780.5049070205</v>
+        <v>550781</v>
       </c>
       <c r="R2" t="n">
-        <v>6998672.072508764</v>
+        <v>6998672</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1999-06-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1999-06-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,7 +784,7 @@
         <v>133729096</v>
       </c>
       <c r="B3" t="n">
-        <v>92238</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,32 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133729086</v>
+        <v>133729089</v>
       </c>
       <c r="B4" t="n">
-        <v>99188</v>
+        <v>80488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550739</v>
+        <v>550773</v>
       </c>
       <c r="R4" t="n">
-        <v>6998590</v>
+        <v>6998677</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +978,7 @@
         <v>133729090</v>
       </c>
       <c r="B5" t="n">
-        <v>80481</v>
+        <v>80488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133729089</v>
+        <v>133729088</v>
       </c>
       <c r="B6" t="n">
-        <v>80481</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,24 +1083,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Granliden, Jmt</t>
@@ -1184,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133729087</v>
+        <v>128709190</v>
       </c>
       <c r="B7" t="n">
-        <v>99210</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,37 +1188,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550719</v>
+        <v>550773</v>
       </c>
       <c r="R7" t="n">
-        <v>6998593</v>
+        <v>6998937</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1249,12 +1242,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1269,68 +1262,64 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133729088</v>
+        <v>128709192</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550773</v>
+        <v>550777</v>
       </c>
       <c r="R8" t="n">
-        <v>6998677</v>
+        <v>6998931</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1354,12 +1343,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,15 +1363,1932 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128709196</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>550780</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6998930</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128709198</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>550773</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6998941</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128709200</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>550782</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6998927</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128709202</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>550771</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6998940</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128709204</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>550784</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6998928</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128709206</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>550761</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6998935</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128709212</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>550792</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6998929</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128709214</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>550765</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6998939</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128709218</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>550769</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6998939</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128709188</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>550802</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6998925</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128709194</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>550777</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6998940</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128709208</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>550759</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6998935</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128709210</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>550762</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6998937</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128709216</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>550794</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6998930</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128709221</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>550770</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6998942</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133729068</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>550587</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6998825</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133729085</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>550735</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6998530</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>på mossig låga över vattnet i dråg</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133729086</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>550739</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6998590</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133729087</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>550719</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6998593</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2288,10 +2288,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128709188</v>
+        <v>134654434</v>
       </c>
       <c r="B18" t="n">
-        <v>99142</v>
+        <v>99112</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550802</v>
+        <v>550770</v>
       </c>
       <c r="R18" t="n">
-        <v>6998925</v>
+        <v>6998920</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2373,26 +2373,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Mika Thunell</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>C250138 Dikesinventering Jämtland 2025</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128709194</v>
+        <v>134654435</v>
       </c>
       <c r="B19" t="n">
-        <v>99142</v>
+        <v>99112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2400,37 +2396,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550777</v>
+        <v>550753</v>
       </c>
       <c r="R19" t="n">
-        <v>6998940</v>
+        <v>6998930</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2454,12 +2450,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2474,26 +2470,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mika Thunell, Magnus Lundin</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>C250138 Dikesinventering Jämtland 2025</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128709208</v>
+        <v>134654437</v>
       </c>
       <c r="B20" t="n">
-        <v>99142</v>
+        <v>99112</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2501,37 +2493,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550759</v>
+        <v>550719</v>
       </c>
       <c r="R20" t="n">
-        <v>6998935</v>
+        <v>6998941</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2555,12 +2547,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2575,26 +2567,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mika Thunell, Magnus Lundin</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>C250138 Dikesinventering Jämtland 2025</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128709210</v>
+        <v>134654438</v>
       </c>
       <c r="B21" t="n">
-        <v>99142</v>
+        <v>99112</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,37 +2590,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550762</v>
+        <v>550649</v>
       </c>
       <c r="R21" t="n">
-        <v>6998937</v>
+        <v>6998965</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2656,12 +2644,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2676,26 +2664,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mika Thunell, Magnus Lundin</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>C250138 Dikesinventering Jämtland 2025</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128709216</v>
+        <v>134654440</v>
       </c>
       <c r="B22" t="n">
-        <v>99142</v>
+        <v>99112</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2703,37 +2687,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550794</v>
+        <v>550611</v>
       </c>
       <c r="R22" t="n">
-        <v>6998930</v>
+        <v>6998985</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2757,12 +2741,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2777,26 +2761,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Mika Thunell</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>C250138 Dikesinventering Jämtland 2025</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128709221</v>
+        <v>134654441</v>
       </c>
       <c r="B23" t="n">
-        <v>99142</v>
+        <v>99112</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2804,37 +2784,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550770</v>
+        <v>550630</v>
       </c>
       <c r="R23" t="n">
-        <v>6998942</v>
+        <v>6998976</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2858,12 +2838,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2878,61 +2858,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mika Thunell, Magnus Lundin</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>C250138 Dikesinventering Jämtland 2025</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133729068</v>
+        <v>134654442</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>99112</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550587</v>
+        <v>550639</v>
       </c>
       <c r="R24" t="n">
-        <v>6998825</v>
+        <v>6998969</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2959,12 +2935,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2979,61 +2955,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133729085</v>
+        <v>134654443</v>
       </c>
       <c r="B25" t="n">
-        <v>99195</v>
+        <v>99112</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550735</v>
+        <v>550673</v>
       </c>
       <c r="R25" t="n">
-        <v>6998530</v>
+        <v>6998956</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3060,17 +3032,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>på mossig låga över vattnet i dråg</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3079,64 +3046,63 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133729086</v>
+        <v>134654444</v>
       </c>
       <c r="B26" t="n">
-        <v>99195</v>
+        <v>99112</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550739</v>
+        <v>550686</v>
       </c>
       <c r="R26" t="n">
-        <v>6998590</v>
+        <v>6998947</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3163,12 +3129,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3183,22 +3149,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133729087</v>
+        <v>134654447</v>
       </c>
       <c r="B27" t="n">
-        <v>99217</v>
+        <v>99112</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,34 +3172,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550719</v>
+        <v>550728</v>
       </c>
       <c r="R27" t="n">
-        <v>6998593</v>
+        <v>6998932</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3260,12 +3226,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3280,15 +3246,5966 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134654448</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>550745</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6998924</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134654449</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>550768</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6998924</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134654450</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>550782</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6998917</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134654451</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>550823</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6998917</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134654453</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>550872</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6998911</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134654454</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>550902</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6998915</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134654457</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>550882</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6998926</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134654462</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>550764</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6998942</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134654464</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>550687</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6998966</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134654465</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>550668</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6998970</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134654466</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>550664</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6998968</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134654467</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>550677</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6998965</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134654468</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>550682</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6998961</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134654469</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>550691</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6998958</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134654470</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>550693</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6998956</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134654471</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>550735</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6998940</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134654472</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>550741</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6998939</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134654473</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>550747</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6998937</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134654474</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>550749</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6998937</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134654475</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>550757</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6998934</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134654477</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>550760</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6998939</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134654479</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>550767</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6998933</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134654481</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>550770</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6998933</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134654483</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>550775</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6998933</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134654485</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>550778</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6998931</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134654487</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>550782</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6998930</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134654488</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>550786</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6998930</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134654491</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>550806</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6998925</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>134654492</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>550810</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6998924</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134654493</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>550867</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6998920</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134654494</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>550892</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6998919</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128709188</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>550802</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6998925</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128709194</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>550777</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6998940</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128709208</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>550759</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6998935</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128709210</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>550762</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6998937</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128709216</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>550794</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6998930</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128709221</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>550770</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6998942</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>134654433</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>550788</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6998923</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>134654436</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>550735</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6998933</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134654439</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>550628</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6998976</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134654445</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>550691</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6998945</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>134654446</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>550695</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6998946</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>134654452</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>550864</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6998911</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>134654463</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>550753</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6998943</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>134654476</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>550760</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6998939</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>134654478</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>550760</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6998935</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>134654480</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>550767</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6998933</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>134654482</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>550771</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6998933</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>134654484</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>550775</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6998933</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>134654486</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>550779</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6998930</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>134654489</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>550806</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6998928</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>134654490</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>550801</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6998932</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>133729068</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>550587</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6998825</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AX80" t="inlineStr">
         <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>133729085</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>550735</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6998530</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>på mossig låga över vattnet i dråg</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>133729086</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>550739</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6998590</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>134654427</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>550700</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6998928</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>134654430</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>550829</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6998830</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134654431</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>550835</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6998837</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>133729087</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>550719</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6998593</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>134654428</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>550682</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6998887</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>134654429</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>550698</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6998829</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6768426</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729096</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729089</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729090</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729088</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1275,6 +1305,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709190</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709192</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709196</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1578,6 +1623,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709198</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1679,6 +1729,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709200</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1780,6 +1835,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709202</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709204</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1982,6 +2047,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709206</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2083,6 +2153,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709212</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2184,6 +2259,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709214</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2285,6 +2365,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709218</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2382,6 +2467,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654434</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2479,6 +2569,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654435</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2576,6 +2671,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654437</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2673,6 +2773,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654438</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2770,6 +2875,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654440</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2867,6 +2977,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654441</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2964,6 +3079,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654442</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3061,6 +3181,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654443</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3158,6 +3283,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654444</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3255,6 +3385,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654447</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3352,6 +3487,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654448</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3449,6 +3589,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654449</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3546,6 +3691,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654450</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3643,6 +3793,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654451</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3740,6 +3895,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654453</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3837,6 +3997,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654454</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3934,6 +4099,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654457</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4031,6 +4201,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654462</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4128,6 +4303,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654464</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4225,6 +4405,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654465</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4322,6 +4507,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654466</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4419,6 +4609,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654467</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4516,6 +4711,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654468</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4613,6 +4813,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654469</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4710,6 +4915,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654470</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4807,6 +5017,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654471</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4904,6 +5119,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654472</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5001,6 +5221,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654473</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5098,6 +5323,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654474</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5195,6 +5425,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654475</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5292,6 +5527,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654477</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5389,6 +5629,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654479</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5486,6 +5731,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654481</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5583,6 +5833,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654483</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5680,6 +5935,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654485</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5777,6 +6037,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654487</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5874,6 +6139,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654488</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5971,6 +6241,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654491</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6068,6 +6343,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654492</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6165,6 +6445,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654493</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6262,6 +6547,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654494</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6363,6 +6653,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709188</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6464,6 +6759,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709194</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6565,6 +6865,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709208</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6666,6 +6971,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709210</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6767,6 +7077,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709216</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6868,6 +7183,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128709221</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6965,6 +7285,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654433</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7062,6 +7387,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654436</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7159,6 +7489,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654439</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7256,6 +7591,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654445</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7353,6 +7693,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654446</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7450,6 +7795,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654452</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7547,6 +7897,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654463</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7644,6 +7999,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654476</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7741,6 +8101,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654478</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7838,6 +8203,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654480</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7935,6 +8305,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654482</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8032,6 +8407,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654484</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8129,6 +8509,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654486</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8226,6 +8611,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654489</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8323,6 +8713,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654490</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8420,6 +8815,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729068</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8527,6 +8927,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729085</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8624,6 +9029,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729086</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8721,6 +9131,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654427</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8818,6 +9233,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654430</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8915,6 +9335,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654431</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9012,6 +9437,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729087</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9109,6 +9539,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654428</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9206,8 +9641,102 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654429</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>